--- a/routing_analytics.xlsx
+++ b/routing_analytics.xlsx
@@ -717,16 +717,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="General">
-                  <c:v>40</c:v>
+                  <c:v>37.37</c:v>
                 </c:pt>
                 <c:pt idx="1" formatCode="General">
-                  <c:v>20</c:v>
+                  <c:v>14.74</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="General">
-                  <c:v>40</c:v>
+                  <c:v>45.79</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="General">
-                  <c:v>0</c:v>
+                  <c:v>2.11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -790,11 +790,11 @@
           </c:val>
           <c:shape val="box"/>
         </c:ser>
-        <c:axId val="5000284"/>
-        <c:axId val="1972391"/>
+        <c:axId val="13901008"/>
+        <c:axId val="1076067"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5000284"/>
+        <c:axId val="13901008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -815,14 +815,14 @@
             <a:endParaRPr/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1972391"/>
+        <c:crossAx val="1076067"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1972391"/>
+        <c:axId val="1076067"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -843,7 +843,7 @@
             <a:endParaRPr/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5000284"/>
+        <c:crossAx val="13901008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -944,24 +944,24 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="General">
-                  <c:v>65.74</c:v>
+                  <c:v>77.11</c:v>
                 </c:pt>
                 <c:pt idx="1" formatCode="General">
-                  <c:v>98.79</c:v>
+                  <c:v>99.98</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="General">
-                  <c:v>16.69</c:v>
+                  <c:v>47.96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:shape val="box"/>
         </c:ser>
-        <c:axId val="5419316"/>
-        <c:axId val="946251"/>
+        <c:axId val="4017457"/>
+        <c:axId val="9236030"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5419316"/>
+        <c:axId val="4017457"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -982,14 +982,14 @@
             <a:endParaRPr/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="946251"/>
+        <c:crossAx val="9236030"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="946251"/>
+        <c:axId val="9236030"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1010,7 +1010,7 @@
             <a:endParaRPr/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5419316"/>
+        <c:crossAx val="4017457"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1106,27 +1106,27 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="General">
-                  <c:v>8</c:v>
+                  <c:v>106</c:v>
                 </c:pt>
                 <c:pt idx="1" formatCode="General">
-                  <c:v>4</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="General">
-                  <c:v>3</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="General">
-                  <c:v>2</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:shape val="box"/>
         </c:ser>
-        <c:axId val="1377927"/>
-        <c:axId val="1961044"/>
+        <c:axId val="12288505"/>
+        <c:axId val="8810312"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1377927"/>
+        <c:axId val="12288505"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1147,14 +1147,14 @@
             <a:endParaRPr/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1961044"/>
+        <c:crossAx val="8810312"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1961044"/>
+        <c:axId val="8810312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1175,7 +1175,7 @@
             <a:endParaRPr/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1377927"/>
+        <c:crossAx val="12288505"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1246,9 +1246,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>'Routing'!$A$13:$A$15</c:f>
+              <c:f>'Routing'!$A$13:$A$16</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1257,35 +1257,41 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Routing'!$B$13:$B$15</c:f>
+              <c:f>'Routing'!$B$13:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="General">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1" formatCode="General">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="General">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="General">
                   <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="2" formatCode="General">
-                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:shape val="box"/>
         </c:ser>
-        <c:axId val="9190249"/>
-        <c:axId val="7205169"/>
+        <c:axId val="2644286"/>
+        <c:axId val="9988779"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="9190249"/>
+        <c:axId val="2644286"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1306,14 +1312,14 @@
             <a:endParaRPr/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7205169"/>
+        <c:crossAx val="9988779"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7205169"/>
+        <c:axId val="9988779"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1334,7 +1340,7 @@
             <a:endParaRPr/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9190249"/>
+        <c:crossAx val="2644286"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1801,7 +1807,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-06T23:59:16+07:00</t>
+          <t>2026-09-07T02:33:18+07:00</t>
         </is>
       </c>
       <c r="E3" s="0"/>
@@ -1847,19 +1853,19 @@
     </row>
     <row customHeight="1" ht="30" r="6">
       <c r="A6" s="22" t="n">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="23" t="n">
-        <v>70.91</v>
+        <v>83.16</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="24" t="n">
-        <v>131.34</v>
+        <v>89.96</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="25" t="n">
-        <v>3777300</v>
+        <v>6887000</v>
       </c>
       <c r="H6" s="13"/>
     </row>
@@ -1909,13 +1915,13 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>40</v>
+        <v>37.37</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>40</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="11">
@@ -1925,13 +1931,13 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>20</v>
+        <v>14.74</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>35</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>-15</v>
+        <v>-20.26</v>
       </c>
     </row>
     <row r="12">
@@ -1941,13 +1947,13 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>40</v>
+        <v>45.79</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>25</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>15</v>
+        <v>20.79</v>
       </c>
     </row>
     <row r="13">
@@ -1957,13 +1963,13 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="14">
@@ -2012,13 +2018,13 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>3287000</v>
+        <v>3855500</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>5000000</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>65.74</v>
+        <v>77.11</v>
       </c>
     </row>
     <row r="18">
@@ -2028,13 +2034,13 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>2963800</v>
+        <v>2999400</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>3000000</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>98.79</v>
+        <v>99.98</v>
       </c>
     </row>
     <row r="19">
@@ -2044,13 +2050,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1335000</v>
+        <v>3837000</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>8000000</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>16.69</v>
+        <v>47.96</v>
       </c>
     </row>
     <row r="20">
@@ -2060,7 +2066,7 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="17"/>
@@ -2101,7 +2107,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>8</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25">
@@ -2111,7 +2117,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26">
@@ -2121,7 +2127,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
@@ -2131,7 +2137,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2297,28 +2303,28 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C2" s="10" t="n">
-        <v>40</v>
+        <v>37.37</v>
       </c>
       <c r="D2" s="10" t="n">
         <v>40</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>0</v>
+        <v>-2.63</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>1306000</v>
+        <v>1874500</v>
       </c>
       <c r="G2" s="10" t="n">
-        <v>34.57</v>
+        <v>27.22</v>
       </c>
       <c r="H2" s="10" t="n">
         <v>50.0</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="J2" s="8" t="n">
         <v>6</v>
@@ -2327,25 +2333,25 @@
         <v>3</v>
       </c>
       <c r="L2" s="10" t="n">
-        <v>79.55</v>
+        <v>87.32</v>
       </c>
       <c r="M2" s="11" t="n">
-        <v>83.93</v>
+        <v>66.46</v>
       </c>
       <c r="N2" s="11" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O2" s="11" t="n">
-        <v>327</v>
+        <v>118</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>3287000</v>
+        <v>3855500</v>
       </c>
       <c r="Q2" s="9" t="n">
         <v>5000000</v>
       </c>
       <c r="R2" s="10" t="n">
-        <v>65.74</v>
+        <v>77.11</v>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -2363,28 +2369,28 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C3" s="10" t="n">
-        <v>20</v>
+        <v>14.74</v>
       </c>
       <c r="D3" s="10" t="n">
         <v>35</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>-15</v>
+        <v>-20.26</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>351300</v>
+        <v>386900</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>9.3</v>
+        <v>5.62</v>
       </c>
       <c r="H3" s="10" t="n">
         <v>65.0</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J3" s="8" t="n">
         <v>3</v>
@@ -2393,25 +2399,25 @@
         <v>7</v>
       </c>
       <c r="L3" s="10" t="n">
-        <v>54.55</v>
+        <v>64.29</v>
       </c>
       <c r="M3" s="11" t="n">
-        <v>247.23</v>
+        <v>205.39</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>101.5</v>
+        <v>67.5</v>
       </c>
       <c r="O3" s="11" t="n">
         <v>689</v>
       </c>
       <c r="P3" s="9" t="n">
-        <v>2963800</v>
+        <v>2999400</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>3000000</v>
       </c>
       <c r="R3" s="10" t="n">
-        <v>98.79</v>
+        <v>99.98</v>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
@@ -2429,28 +2435,28 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>40</v>
+        <v>45.79</v>
       </c>
       <c r="D4" s="10" t="n">
         <v>25</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>15</v>
+        <v>20.79</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>2120000</v>
+        <v>4622000</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>56.12</v>
+        <v>67.11</v>
       </c>
       <c r="H4" s="10" t="n">
         <v>25.0</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="J4" s="8" t="n">
         <v>7</v>
@@ -2459,25 +2465,25 @@
         <v>6</v>
       </c>
       <c r="L4" s="10" t="n">
-        <v>70.45</v>
+        <v>85.06</v>
       </c>
       <c r="M4" s="11" t="n">
-        <v>120.8</v>
+        <v>75.43</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="O4" s="11" t="n">
-        <v>522</v>
+        <v>419</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>1335000</v>
+        <v>3837000</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>8000000</v>
       </c>
       <c r="R4" s="10" t="n">
-        <v>16.69</v>
+        <v>47.96</v>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
@@ -2495,26 +2501,26 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>0</v>
@@ -2522,12 +2528,20 @@
       <c r="K5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="10"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
+      <c r="L5" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="O5" s="11" t="n">
+        <v>15</v>
+      </c>
       <c r="P5" s="9" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="Q5" s="9"/>
       <c r="R5" s="10"/>
@@ -2554,7 +2568,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="52" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -2592,7 +2606,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
@@ -2602,7 +2616,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>24</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6">
@@ -2612,7 +2626,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="7">
@@ -2622,7 +2636,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
@@ -2642,7 +2656,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -2681,7 +2695,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="8" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -2689,93 +2703,101 @@
         <v>3</v>
       </c>
       <c r="B15" s="8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>selected</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
           <t>skipped</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="B20" s="8" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Skip reason</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>bank_not_in_list</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>daily_amount_limit_exceeded</t>
+          <t>bank_not_in_list</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>4</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>amount_exceeds_limit</t>
+          <t>daily_amount_limit_exceeded</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>amount_exceeds_limit</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
           <t>amount_below_minimum</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
-        <v>2</v>
+      <c r="B26" s="8" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2859,21 +2881,23 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="C3" s="18" t="n">
-        <v>58.33</v>
+        <v>39</v>
+      </c>
+      <c r="C3" s="19" t="n">
+        <v>74.36</v>
       </c>
       <c r="D3" s="19" t="n">
         <v>62.5</v>
       </c>
-      <c r="E3" s="18" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="F3" s="19" t="n">
-        <v>75</v>
-      </c>
-      <c r="G3" s="17"/>
+      <c r="E3" s="19" t="n">
+        <v>61.54</v>
+      </c>
+      <c r="F3" s="20" t="n">
+        <v>88.24</v>
+      </c>
+      <c r="G3" s="20" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2882,17 +2906,17 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="C4" s="19" t="n">
-        <v>72.73</v>
+        <v>27</v>
+      </c>
+      <c r="C4" s="20" t="n">
+        <v>88.89</v>
       </c>
       <c r="D4" s="20" t="n">
         <v>80</v>
       </c>
       <c r="E4" s="17"/>
-      <c r="F4" s="19" t="n">
-        <v>66.67</v>
+      <c r="F4" s="20" t="n">
+        <v>90.91</v>
       </c>
       <c r="G4" s="17"/>
     </row>
@@ -2903,10 +2927,10 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>73.68</v>
+        <v>33</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>84.85</v>
       </c>
       <c r="D5" s="20" t="n">
         <v>85.71</v>
@@ -2914,10 +2938,12 @@
       <c r="E5" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="F5" s="19" t="n">
-        <v>75</v>
-      </c>
-      <c r="G5" s="17"/>
+      <c r="F5" s="20" t="n">
+        <v>90.48</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -2926,21 +2952,23 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>75</v>
+        <v>32</v>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>84.38</v>
       </c>
       <c r="D6" s="20" t="n">
-        <v>88.89</v>
+        <v>94.12</v>
       </c>
       <c r="E6" s="20" t="n">
         <v>100</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="G6" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -2949,21 +2977,23 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>66.67</v>
+        <v>27</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>81.48</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>85.71</v>
+        <v>93.75</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="G7" s="17"/>
+        <v>75</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2972,19 +3002,19 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C8" s="20" t="n">
-        <v>80.95</v>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>75</v>
+        <v>87.5</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>88.89</v>
       </c>
       <c r="E8" s="19" t="n">
         <v>66.67</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="G8" s="17"/>
     </row>
@@ -3040,7 +3070,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>100</v>
@@ -3050,7 +3080,9 @@
         <v>100</v>
       </c>
       <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+      <c r="G12" s="20" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -3059,19 +3091,19 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>61.76</v>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>63.64</v>
+        <v>77.19</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>83.33</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>50</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>69.23</v>
+        <v>58.33</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>80.95</v>
       </c>
       <c r="G13" s="17"/>
     </row>
@@ -3082,19 +3114,19 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>47</v>
-      </c>
-      <c r="C14" s="19" t="n">
-        <v>74.47</v>
-      </c>
-      <c r="D14" s="19" t="n">
-        <v>79.17</v>
+        <v>76</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <v>84.21</v>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>85.71</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>83.33</v>
+        <v>93.1</v>
       </c>
       <c r="G14" s="17"/>
     </row>
@@ -3105,17 +3137,17 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C15" s="20" t="n">
-        <v>81.82</v>
+        <v>88.24</v>
       </c>
       <c r="D15" s="20" t="n">
         <v>100</v>
       </c>
       <c r="E15" s="17"/>
-      <c r="F15" s="19" t="n">
-        <v>69.23</v>
+      <c r="F15" s="20" t="n">
+        <v>81.82</v>
       </c>
       <c r="G15" s="17"/>
     </row>
@@ -3126,15 +3158,15 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>50</v>
+        <v>15</v>
+      </c>
+      <c r="C16" s="20" t="n">
+        <v>80</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
-      <c r="F16" s="18" t="n">
-        <v>50</v>
+      <c r="F16" s="20" t="n">
+        <v>80</v>
       </c>
       <c r="G16" s="17"/>
     </row>
@@ -3171,7 +3203,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="24" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -3219,14 +3251,14 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>100</v>
       </c>
       <c r="D4" s="9" t="str">
         <f>B4-C4</f>
-        <v>-90</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="5">
@@ -3236,14 +3268,14 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>385800</v>
+        <v>3495500</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>3391500</v>
       </c>
       <c r="D5" s="9" t="str">
         <f>B5-C5</f>
-        <v>-3005700</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="6">
@@ -3270,14 +3302,14 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>38.6</v>
+        <v>33.68</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>140.61</v>
       </c>
       <c r="D7" s="9" t="str">
         <f>B7-C7</f>
-        <v>-102.01000000000002</v>
+        <v>-106.93</v>
       </c>
     </row>
     <row r="8"/>
@@ -3320,13 +3352,13 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>19</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>11</v>
+        <v>-9</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>100</v>
@@ -3342,13 +3374,13 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>40</v>
+        <v>52.22</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>40</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0</v>
+        <v>12.219999999999999</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>100</v>
@@ -3360,72 +3392,88 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>vipay</t>
+          <t>spacepayments</t>
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>-11</v>
-      </c>
+        <v>4.44</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9"/>
       <c r="E12" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>vipay</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>-7.670000000000002</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" s="10" t="n">
         <v>78.05</v>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>From (inclusive)</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>To (exclusive)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-30T00:00:00.000000Z</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-31T00:00:00.000000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30T00:00:00.000000Z</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:00:00.000000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
           <t>Previous</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>2026-07-29T00:00:00.000000Z</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>2026-07-30T00:00:00.000000Z</t>
         </is>
@@ -3448,7 +3496,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="9.9" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -3480,27 +3528,27 @@
       </c>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t>vipay: доля количества ниже цели на 10 п.п.; повысить вес распределения по количеству среди допустимых провайдеров.</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="38" r="4">
+          <t>payflow: дневной лимит использован на 99.98%, доля количества ниже цели на 25 п.п.; увеличить доступную ёмкость или снизить целевую долю.</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="40" r="4">
       <c r="A4" s="8" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>vipay: доля суммы ниже цели на 27.45 п.п.; повысить вес распределения по объёму для провайдера.</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="40" r="5">
+          <t>quickpay: доля количества выше цели на 27.22 п.п.; снизить вес распределения по количеству среди допустимых провайдеров.</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="38" r="5">
       <c r="A5" s="8" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>payflow: дневной лимит использован на 98.79%, доля количества ниже цели на 5 п.п.; увеличить доступную ёмкость или снизить целевую долю.</t>
+          <t>quickpay: доля суммы выше цели на 53.3 п.п.; снизить вес распределения по объёму.</t>
         </is>
       </c>
     </row>
@@ -3510,17 +3558,17 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>quickpay: доля количества выше цели на 15 п.п.; снизить вес распределения по количеству среди допустимых провайдеров.</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="38" r="7">
+          <t>vipay: среди пропусков доминирует причина «банк не входит в список доступных» (41); скорректировать правила провайдера либо стратегию маршрутизации по этой причине.</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="40" r="7">
       <c r="A7" s="8" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>quickpay: доля суммы выше цели на 35.91 п.п.; снизить вес распределения по объёму.</t>
+          <t>vipay: частые пропуски по причине «банк не входит в список доступных» (41 из 89 операций); не увеличивать глобальную долю провайдера; учитывать доступность по банкам.</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3578,7 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>Для 50% операций с проверкой доступности имеется не более одного допустимого провайдера; высок риск отсутствия маршрута, расширить покрытие провайдеров и пересмотреть ограничения.</t>
+          <t>payflow: частые пропуски по причине «сумма превышает допустимый предел» (23 из 90 операций); перенаправлять крупные операции к провайдерам с большим диапазоном сумм.</t>
         </is>
       </c>
     </row>
@@ -3540,18 +3588,48 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>Для 3 операций оценка выбранного провайдера значительно выше второй; сохранить выбор, имеется сильное основание для маршрута.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+          <t>payflow: среди пропусков доминирует причина «дневной лимит суммы исчерпан» (45); скорректировать правила провайдера либо стратегию маршрутизации по этой причине.</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="40" r="10">
+      <c r="A10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>payflow: частые пропуски по причине «дневной лимит суммы исчерпан» (45 из 90 операций); уменьшить целевую долю либо увеличить дневной лимит; дальнейшее повышение веса бессмысленно.</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="40" r="11">
+      <c r="A11" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>quickpay: среди пропусков доминирует причина «код причины «amount_below_minimum»» (8); скорректировать правила провайдера либо стратегию маршрутизации по этой причине.</t>
+        </is>
+      </c>
+    </row>
+    <row customHeight="1" ht="40" r="12">
+      <c r="A12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Для 61.11% операций с проверкой доступности имеется не более одного допустимого провайдера; высок риск отсутствия маршрута, расширить покрытие провайдеров и пересмотреть ограничения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
